--- a/output/clubs_aggregate.xlsx
+++ b/output/clubs_aggregate.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,9 +38,15 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -49,7 +55,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="000B5CAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2E5EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCF4DD"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,18 +86,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -442,14 +464,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,369 +490,377 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Показатель</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Среднее по клубам</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>club a</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>club b</t>
-        </is>
-      </c>
+          <t>Средняя цена билета (регулярный чемпионат), руб.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Посещаемость за сезон (всего проходов)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>387093</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>чел.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>387093</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>387093</v>
+          <t>Среднее по Лиге</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1116.5207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Средняя посещаемость (сезон)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>8797.5682</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>зрит./матч</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>8797.5682</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>8797.5682</v>
+          <t>Минимум</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1116.5207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Средняя посещаемость (регулярка)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>8789.3529</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>зрит./матч</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>8789.3529</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>8789.3529</v>
+          <t>Максимум</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1116.5207</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Матчей за сезон</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>44</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Клуб</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Градация</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Платные билеты (разовые)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>234277</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>234277</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>234277</v>
+          <t>club a</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1116.5207</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Хорошие показатели</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Бесплатные билеты (разовые)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>19960</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>19960</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>19960</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Доля бесплатных билетов</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0.0927</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0.0927</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>0.0927</v>
+          <t>club b</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>1116.5207</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Удовлетворительные показатели</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Платных абонементов (продано)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>2479</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>2479</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>2479</v>
-      </c>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Доля продаж билетов онлайн, %</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Заполняемость арены (регулярка)</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0.9804</v>
+          <t>Среднее по Лиге</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>0.8476</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Доход — всего за сезон</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>510511394.8</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>руб.</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>510511394.8</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>510511394.8</v>
+          <t>Минимум</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0.8476</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Доход от платных билетов</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>379145691.8</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>руб.</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>379145691.8</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>379145691.8</v>
+          <t>Максимум</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>0.8476</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Доход от абонементов</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>78873675</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>руб.</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>78873675</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>78873675</v>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Клуб</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Градация</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Средняя цена платного билета (сезон)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>1618.365</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>руб.</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1618.365</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>1618.365</v>
+          <t>club a</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Хорошие показатели</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Стоимость абонемента (сезон)</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>31816.7305</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>руб.</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>31816.7305</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>31816.7305</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Доля онлайн-продаж</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
+          <t>club b</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
         <v>0.8476</v>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>0.8476</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>0.8476</v>
+      <c r="C18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Удовлетворительные показатели</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Агентская комиссия (средняя)</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Доля бесплатных билетов, %</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Среднее по Лиге</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>0.0927</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Минимум</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>0.0927</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Максимум</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>0.0927</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Клуб</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Градация</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>club a</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Хорошие показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>club b</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Удовлетворительные показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Фактическое отклонение посещаемости, %</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Нет данных по параметру</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Клуб</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Градация</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>club a</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>club b</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>нет данных</t>
         </is>
       </c>
     </row>

--- a/output/clubs_aggregate.xlsx
+++ b/output/clubs_aggregate.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Доля продаж билетов онлайн, %</t>
+          <t>Общая выручка (за сезон), руб.</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -601,8 +601,8 @@
           <t>Среднее по Лиге</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>0.8476</v>
+      <c r="B13" s="5" t="n">
+        <v>510511394.8</v>
       </c>
     </row>
     <row r="14">
@@ -611,8 +611,8 @@
           <t>Минимум</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v>0.8476</v>
+      <c r="B14" s="5" t="n">
+        <v>510511394.8</v>
       </c>
     </row>
     <row r="15">
@@ -621,8 +621,8 @@
           <t>Максимум</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0.8476</v>
+      <c r="B15" s="5" t="n">
+        <v>510511394.8</v>
       </c>
     </row>
     <row r="16">
@@ -653,8 +653,8 @@
           <t>club a</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
-        <v>0.8476</v>
+      <c r="B17" s="7" t="n">
+        <v>510511394.8</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>1</v>
@@ -671,8 +671,8 @@
           <t>club b</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
-        <v>0.8476</v>
+      <c r="B18" s="7" t="n">
+        <v>510511394.8</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>2</v>
@@ -686,7 +686,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Доля бесплатных билетов, %</t>
+          <t>Доля продаж билетов онлайн, %</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>0.0927</v>
+        <v>0.8476</v>
       </c>
     </row>
     <row r="22">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>0.0927</v>
+        <v>0.8476</v>
       </c>
     </row>
     <row r="23">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>0.0927</v>
+        <v>0.8476</v>
       </c>
     </row>
     <row r="24">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>0.0927</v>
+        <v>0.8476</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>1</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>0.0927</v>
+        <v>0.8476</v>
       </c>
       <c r="C26" s="2" t="n">
         <v>2</v>
@@ -784,7 +784,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Фактическое отклонение посещаемости, %</t>
+          <t>Доля бесплатных билетов, %</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -794,71 +794,252 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Нет данных по параметру</t>
-        </is>
+          <t>Среднее по Лиге</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>0.0927</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Клуб</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Значение</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Место</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Градация</t>
-        </is>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Минимум</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>0.0927</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>Максимум</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>0.0927</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Клуб</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Градация</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>club a</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="11" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Хорошие показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>club b</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Удовлетворительные показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Агентская комиссия (средняя), %</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Нет данных по параметру</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Клуб</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Градация</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>club a</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>club b</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Фактическое отклонение посещаемости, %</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Нет данных по параметру</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Клуб</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Градация</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>club a</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>club b</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
